--- a/output/graficos_dimensiones/comunal_o_ocup_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2021_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:52</t>
+    <t xml:space="preserve">2026-09-09 22:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2021_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:40</t>
+    <t xml:space="preserve">2026-09-18 10:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2021_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:03</t>
+    <t xml:space="preserve">2026-09-23 12:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2021_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:08</t>
+    <t xml:space="preserve">2026-10-02 13:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2021_biobio.xlsx
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Concepción</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Lota</t>
@@ -93,7 +93,7 @@
     <t xml:space="preserve">Tucapel</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">San Rosendo</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:37</t>
+    <t xml:space="preserve">2026-10-04 08:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2021_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:25</t>
+    <t xml:space="preserve">2026-10-05 08:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
